--- a/DesignTable/Data/Table/Tables/passive.xlsx
+++ b/DesignTable/Data/Table/Tables/passive.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Oh\Desktop\DesignGenerator\Data\Data_Export\Table\Tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E39DF9C-A7A5-4CF4-8005-646D70C9FCA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{19CDE2EB-A902-4F97-9656-F8841076D7CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-240" yWindow="0" windowWidth="29040" windowHeight="15600" activeTab="1" xr2:uid="{45DB0937-A2ED-4242-B08C-63C8CC7A40EE}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{45DB0937-A2ED-4242-B08C-63C8CC7A40EE}"/>
   </bookViews>
   <sheets>
     <sheet name="record" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="26">
   <si>
     <t>ColumnName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,10 +61,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TableID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>passive_Id</t>
   </si>
   <si>
@@ -115,6 +111,14 @@
   </si>
   <si>
     <t>image_Res</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FieldNo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TableId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -172,7 +176,11 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -187,7 +195,7 @@
 
 <file path=xl/xmlMaps.xml><?xml version="1.0" encoding="utf-8"?>
 <MapInfo xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" SelectionNamespaces="">
-  <Schema ID="Schema1">
+  <Schema ID="Schema2">
     <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="">
       <xsd:element nillable="true" name="passive">
         <xsd:complexType>
@@ -202,6 +210,7 @@
                 <xsd:attribute name="EnumID" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="IDRule" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="StringHashIds" form="unqualified" type="xsd:string"/>
+                <xsd:attribute name="FieldNo" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="TableId" form="unqualified" type="xsd:string"/>
               </xsd:complexType>
             </xsd:element>
@@ -221,7 +230,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="1" Name="passive_맵" RootElement="passive" SchemaID="Schema1" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="4" Name="passive_맵" RootElement="passive" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -230,19 +239,19 @@
   <autoFilter ref="A1:E2" xr:uid="{1C1E8E21-5597-45F7-B267-F6B6B8174F41}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{928B96FD-7BBD-4C7E-B177-870CEFB8E486}" uniqueName="passive_Id" name="passive_Id">
-      <xmlColumnPr mapId="1" xpath="/passive/record/passive_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/passive/record/passive_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{4DB59B07-5539-4160-AF5B-72270A04F453}" uniqueName="status_Type" name="status_Type">
-      <xmlColumnPr mapId="1" xpath="/passive/record/status_Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/passive/record/status_Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{780CA10F-636C-4D9B-8327-300D007F344F}" uniqueName="status_Arg" name="status_Arg">
-      <xmlColumnPr mapId="1" xpath="/passive/record/status_Arg" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/passive/record/status_Arg" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{7CD7A30D-2463-4087-BB3D-7B14FCA687FA}" uniqueName="passive_name" name="passive_name">
-      <xmlColumnPr mapId="1" xpath="/passive/record/passive_name" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/passive/record/passive_name" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{704F191A-7841-4A9E-BB7E-89D296ADA0FD}" uniqueName="image_Res" name="image_Res">
-      <xmlColumnPr mapId="1" xpath="/passive/record/image_Res" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/passive/record/image_Res" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -250,35 +259,38 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D2639BA8-67B8-4DF0-AE6C-3BCAF12D9756}" name="표1" displayName="표1" ref="A1:I6" tableType="xml" totalsRowShown="0">
-  <autoFilter ref="A1:I6" xr:uid="{D2639BA8-67B8-4DF0-AE6C-3BCAF12D9756}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D2639BA8-67B8-4DF0-AE6C-3BCAF12D9756}" name="표1" displayName="표1" ref="A1:J6" tableType="xml" totalsRowShown="0">
+  <autoFilter ref="A1:J6" xr:uid="{D2639BA8-67B8-4DF0-AE6C-3BCAF12D9756}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{B53977CC-55B8-4497-AC26-8913F6E6A3AC}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="1" xpath="/passive/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/passive/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{BEB56F1E-129A-4724-9C3C-647A5DD0E6F6}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="1" xpath="/passive/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/passive/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{08C9B5D3-8AAA-4626-9CEB-49ADF4312BC4}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="1" xpath="/passive/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/passive/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{4F4AA0BC-1B98-457D-B69A-474A6B5A02B5}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="1" xpath="/passive/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/passive/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{526469BB-7DDA-4C8D-8F72-E3363BBC4052}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="1" xpath="/passive/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/passive/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{2575B694-8A43-4A99-B06F-0BA6D8CF1F7D}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="1" xpath="/passive/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/passive/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{BDD9855F-535B-42E7-BE5A-4BB25F526BE8}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="1" xpath="/passive/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/passive/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{E400C7E4-7AD7-4E29-AF24-55256F5FDB65}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="1" xpath="/passive/verify/@StringHashIds" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{87A3ED46-2392-43C7-9CF8-E50E806D2698}" uniqueName="TableId" name="TableID">
-      <xmlColumnPr mapId="1" xpath="/passive/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/passive/verify/@StringHashIds" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{87A3ED46-2392-43C7-9CF8-E50E806D2698}" uniqueName="FieldNo" name="FieldNo">
+      <xmlColumnPr mapId="4" xpath="/passive/verify/@FieldNo" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{E7AB5C57-E31E-4B00-B7B8-B939C1E402FF}" uniqueName="TableId" name="TableId" dataDxfId="0">
+      <xmlColumnPr mapId="4" xpath="/passive/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -587,19 +599,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -620,10 +632,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3177CE2-4297-421D-A2F8-0FC932226A55}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -649,151 +661,169 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1021</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1">
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="1">
         <v>1021</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="1">
         <v>1021</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="1">
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="1">
         <v>1021</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="1">
+        <v>11</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" s="1">
         <v>1021</v>
       </c>
     </row>

--- a/DesignTable/Data/Table/Tables/passive.xlsx
+++ b/DesignTable/Data/Table/Tables/passive.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19CDE2EB-A902-4F97-9656-F8841076D7CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{88A55690-020C-4D4D-A1EB-C6DA832CFA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{45DB0937-A2ED-4242-B08C-63C8CC7A40EE}"/>
   </bookViews>
@@ -230,7 +230,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="4" Name="passive_맵" RootElement="passive" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="6" Name="passive_맵" RootElement="passive" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -239,19 +239,19 @@
   <autoFilter ref="A1:E2" xr:uid="{1C1E8E21-5597-45F7-B267-F6B6B8174F41}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{928B96FD-7BBD-4C7E-B177-870CEFB8E486}" uniqueName="passive_Id" name="passive_Id">
-      <xmlColumnPr mapId="4" xpath="/passive/record/passive_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/passive/record/passive_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{4DB59B07-5539-4160-AF5B-72270A04F453}" uniqueName="status_Type" name="status_Type">
-      <xmlColumnPr mapId="4" xpath="/passive/record/status_Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/passive/record/status_Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{780CA10F-636C-4D9B-8327-300D007F344F}" uniqueName="status_Arg" name="status_Arg">
-      <xmlColumnPr mapId="4" xpath="/passive/record/status_Arg" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/passive/record/status_Arg" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{7CD7A30D-2463-4087-BB3D-7B14FCA687FA}" uniqueName="passive_name" name="passive_name">
-      <xmlColumnPr mapId="4" xpath="/passive/record/passive_name" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/passive/record/passive_name" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{704F191A-7841-4A9E-BB7E-89D296ADA0FD}" uniqueName="image_Res" name="image_Res">
-      <xmlColumnPr mapId="4" xpath="/passive/record/image_Res" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/passive/record/image_Res" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -263,34 +263,34 @@
   <autoFilter ref="A1:J6" xr:uid="{D2639BA8-67B8-4DF0-AE6C-3BCAF12D9756}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{B53977CC-55B8-4497-AC26-8913F6E6A3AC}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="4" xpath="/passive/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/passive/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{BEB56F1E-129A-4724-9C3C-647A5DD0E6F6}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="4" xpath="/passive/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/passive/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{08C9B5D3-8AAA-4626-9CEB-49ADF4312BC4}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="4" xpath="/passive/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/passive/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{4F4AA0BC-1B98-457D-B69A-474A6B5A02B5}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="4" xpath="/passive/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/passive/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{526469BB-7DDA-4C8D-8F72-E3363BBC4052}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="4" xpath="/passive/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/passive/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{2575B694-8A43-4A99-B06F-0BA6D8CF1F7D}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="4" xpath="/passive/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/passive/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{BDD9855F-535B-42E7-BE5A-4BB25F526BE8}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="4" xpath="/passive/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/passive/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{E400C7E4-7AD7-4E29-AF24-55256F5FDB65}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="4" xpath="/passive/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/passive/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{87A3ED46-2392-43C7-9CF8-E50E806D2698}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="4" xpath="/passive/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/passive/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{E7AB5C57-E31E-4B00-B7B8-B939C1E402FF}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="4" xpath="/passive/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/passive/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/passive.xlsx
+++ b/DesignTable/Data/Table/Tables/passive.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{88A55690-020C-4D4D-A1EB-C6DA832CFA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B7A0350-4E94-4864-87B4-6748B7E1D7C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{45DB0937-A2ED-4242-B08C-63C8CC7A40EE}"/>
   </bookViews>
@@ -230,7 +230,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="6" Name="passive_맵" RootElement="passive" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="8" Name="passive_맵" RootElement="passive" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -239,19 +239,19 @@
   <autoFilter ref="A1:E2" xr:uid="{1C1E8E21-5597-45F7-B267-F6B6B8174F41}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{928B96FD-7BBD-4C7E-B177-870CEFB8E486}" uniqueName="passive_Id" name="passive_Id">
-      <xmlColumnPr mapId="6" xpath="/passive/record/passive_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/passive/record/passive_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{4DB59B07-5539-4160-AF5B-72270A04F453}" uniqueName="status_Type" name="status_Type">
-      <xmlColumnPr mapId="6" xpath="/passive/record/status_Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/passive/record/status_Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{780CA10F-636C-4D9B-8327-300D007F344F}" uniqueName="status_Arg" name="status_Arg">
-      <xmlColumnPr mapId="6" xpath="/passive/record/status_Arg" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/passive/record/status_Arg" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{7CD7A30D-2463-4087-BB3D-7B14FCA687FA}" uniqueName="passive_name" name="passive_name">
-      <xmlColumnPr mapId="6" xpath="/passive/record/passive_name" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/passive/record/passive_name" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{704F191A-7841-4A9E-BB7E-89D296ADA0FD}" uniqueName="image_Res" name="image_Res">
-      <xmlColumnPr mapId="6" xpath="/passive/record/image_Res" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/passive/record/image_Res" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -263,34 +263,34 @@
   <autoFilter ref="A1:J6" xr:uid="{D2639BA8-67B8-4DF0-AE6C-3BCAF12D9756}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{B53977CC-55B8-4497-AC26-8913F6E6A3AC}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="6" xpath="/passive/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/passive/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{BEB56F1E-129A-4724-9C3C-647A5DD0E6F6}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="6" xpath="/passive/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/passive/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{08C9B5D3-8AAA-4626-9CEB-49ADF4312BC4}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="6" xpath="/passive/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/passive/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{4F4AA0BC-1B98-457D-B69A-474A6B5A02B5}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="6" xpath="/passive/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/passive/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{526469BB-7DDA-4C8D-8F72-E3363BBC4052}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="6" xpath="/passive/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/passive/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{2575B694-8A43-4A99-B06F-0BA6D8CF1F7D}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="6" xpath="/passive/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/passive/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{BDD9855F-535B-42E7-BE5A-4BB25F526BE8}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="6" xpath="/passive/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/passive/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{E400C7E4-7AD7-4E29-AF24-55256F5FDB65}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="6" xpath="/passive/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/passive/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{87A3ED46-2392-43C7-9CF8-E50E806D2698}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="6" xpath="/passive/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/passive/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{E7AB5C57-E31E-4B00-B7B8-B939C1E402FF}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="6" xpath="/passive/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/passive/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/passive.xlsx
+++ b/DesignTable/Data/Table/Tables/passive.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B7A0350-4E94-4864-87B4-6748B7E1D7C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EBC2C13-D1A2-464F-B5E0-7F5247F5401D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{45DB0937-A2ED-4242-B08C-63C8CC7A40EE}"/>
   </bookViews>
@@ -230,7 +230,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="8" Name="passive_맵" RootElement="passive" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="9" Name="passive_맵" RootElement="passive" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -239,19 +239,19 @@
   <autoFilter ref="A1:E2" xr:uid="{1C1E8E21-5597-45F7-B267-F6B6B8174F41}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{928B96FD-7BBD-4C7E-B177-870CEFB8E486}" uniqueName="passive_Id" name="passive_Id">
-      <xmlColumnPr mapId="8" xpath="/passive/record/passive_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/passive/record/passive_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{4DB59B07-5539-4160-AF5B-72270A04F453}" uniqueName="status_Type" name="status_Type">
-      <xmlColumnPr mapId="8" xpath="/passive/record/status_Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/passive/record/status_Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{780CA10F-636C-4D9B-8327-300D007F344F}" uniqueName="status_Arg" name="status_Arg">
-      <xmlColumnPr mapId="8" xpath="/passive/record/status_Arg" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/passive/record/status_Arg" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{7CD7A30D-2463-4087-BB3D-7B14FCA687FA}" uniqueName="passive_name" name="passive_name">
-      <xmlColumnPr mapId="8" xpath="/passive/record/passive_name" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/passive/record/passive_name" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{704F191A-7841-4A9E-BB7E-89D296ADA0FD}" uniqueName="image_Res" name="image_Res">
-      <xmlColumnPr mapId="8" xpath="/passive/record/image_Res" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/passive/record/image_Res" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -263,34 +263,34 @@
   <autoFilter ref="A1:J6" xr:uid="{D2639BA8-67B8-4DF0-AE6C-3BCAF12D9756}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{B53977CC-55B8-4497-AC26-8913F6E6A3AC}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="8" xpath="/passive/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/passive/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{BEB56F1E-129A-4724-9C3C-647A5DD0E6F6}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="8" xpath="/passive/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/passive/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{08C9B5D3-8AAA-4626-9CEB-49ADF4312BC4}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="8" xpath="/passive/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/passive/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{4F4AA0BC-1B98-457D-B69A-474A6B5A02B5}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="8" xpath="/passive/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/passive/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{526469BB-7DDA-4C8D-8F72-E3363BBC4052}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="8" xpath="/passive/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/passive/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{2575B694-8A43-4A99-B06F-0BA6D8CF1F7D}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="8" xpath="/passive/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/passive/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{BDD9855F-535B-42E7-BE5A-4BB25F526BE8}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="8" xpath="/passive/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/passive/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{E400C7E4-7AD7-4E29-AF24-55256F5FDB65}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="8" xpath="/passive/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/passive/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{87A3ED46-2392-43C7-9CF8-E50E806D2698}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="8" xpath="/passive/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/passive/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{E7AB5C57-E31E-4B00-B7B8-B939C1E402FF}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="8" xpath="/passive/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/passive/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
